--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2359,7 +2359,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-patient-contact-role</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-role-informateur-cisis</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelationType</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
